--- a/excel/X_test_scaled.xlsx
+++ b/excel/X_test_scaled.xlsx
@@ -471,7 +471,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.38154514129737</v>
+        <v>1.38156494217898</v>
       </c>
       <c r="B2" t="n">
         <v>-0.5971068087018129</v>
@@ -501,7 +501,7 @@
         <v>-0.6309473049863821</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5751323293844505</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L2" t="n">
         <v>0.9777236966047054</v>
@@ -524,7 +524,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.317809484276268</v>
+        <v>1.317736861151459</v>
       </c>
       <c r="B3" t="n">
         <v>-0.499118678996904</v>
@@ -554,7 +554,7 @@
         <v>-0.6381781142170829</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L3" t="n">
         <v>0.7657668001201835</v>
@@ -577,7 +577,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.8364254208228723</v>
+        <v>-0.8364214189227441</v>
       </c>
       <c r="B4" t="n">
         <v>0.6803680674510756</v>
@@ -607,7 +607,7 @@
         <v>1.968930325074485</v>
       </c>
       <c r="K4" t="n">
-        <v>2.525320471176772</v>
+        <v>2.523288928260168</v>
       </c>
       <c r="L4" t="n">
         <v>-1.004073285525573</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.381197928427309</v>
+        <v>1.38156494217898</v>
       </c>
       <c r="B5" t="n">
         <v>-0.5971068087018129</v>
@@ -660,7 +660,7 @@
         <v>-0.6309473049863821</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2271223211581907</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L5" t="n">
         <v>0.9777236966047054</v>
@@ -683,7 +683,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.317809484276268</v>
+        <v>1.317736861151459</v>
       </c>
       <c r="B6" t="n">
         <v>-0.499118678996904</v>
@@ -713,7 +713,7 @@
         <v>-0.6381781142170829</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L6" t="n">
         <v>0.7657668001201835</v>
@@ -736,7 +736,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1658550323054795</v>
+        <v>0.1658233836066257</v>
       </c>
       <c r="B7" t="n">
         <v>0.582379937746166</v>
@@ -766,7 +766,7 @@
         <v>-0.6217079376360422</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L7" t="n">
         <v>-0.4720614753494234</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.317809484276268</v>
+        <v>1.317736861151459</v>
       </c>
       <c r="B8" t="n">
         <v>-0.499118678996904</v>
@@ -819,7 +819,7 @@
         <v>-0.6381781142170829</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L8" t="n">
         <v>0.7657668001201835</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.25336824970097</v>
+        <v>2.253262349233212</v>
       </c>
       <c r="B9" t="n">
         <v>-3.105965848146391</v>
@@ -872,7 +872,7 @@
         <v>-0.6353661328495881</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L9" t="n">
         <v>-1.175758371678036</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.381639835716482</v>
+        <v>1.38156494217898</v>
       </c>
       <c r="B10" t="n">
         <v>-0.5971068087018129</v>
@@ -925,7 +925,7 @@
         <v>-0.6309473049863821</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L10" t="n">
         <v>0.9777236966047054</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2.25336824970097</v>
+        <v>2.253262349233212</v>
       </c>
       <c r="B11" t="n">
         <v>-3.105965848146391</v>
@@ -978,7 +978,7 @@
         <v>-0.6353661328495881</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L11" t="n">
         <v>-1.175758371678036</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1658550323054795</v>
+        <v>0.1658233836066257</v>
       </c>
       <c r="B12" t="n">
         <v>0.582379937746166</v>
@@ -1031,7 +1031,7 @@
         <v>-0.6217079376360422</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L12" t="n">
         <v>-0.4720614753494234</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.2754872468321777</v>
+        <v>-0.275503197213701</v>
       </c>
       <c r="B13" t="n">
         <v>0.01259710946206584</v>
@@ -1084,7 +1084,7 @@
         <v>-0.5256988595172926</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L13" t="n">
         <v>-0.3491264753884007</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.435741768769646</v>
+        <v>-0.4357520189804448</v>
       </c>
       <c r="B14" t="n">
         <v>0.09606847921069157</v>
@@ -1137,7 +1137,7 @@
         <v>-0.6020240680635789</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4485832354839924</v>
+        <v>-0.4181600802070733</v>
       </c>
       <c r="L14" t="n">
         <v>1.677181455003627</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.02377868235614849</v>
+        <v>0.02375208723981349</v>
       </c>
       <c r="B15" t="n">
         <v>0.7710978171778432</v>
@@ -1190,7 +1190,7 @@
         <v>-0.6100583005421354</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L15" t="n">
         <v>-0.5610833718729226</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.381608270910111</v>
+        <v>1.38156494217898</v>
       </c>
       <c r="B16" t="n">
         <v>-0.5971068087018129</v>
@@ -1243,7 +1243,7 @@
         <v>-0.6309473049863821</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6384068763346795</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L16" t="n">
         <v>0.9777236966047054</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.4365308889288804</v>
+        <v>-0.436541111071082</v>
       </c>
       <c r="B17" t="n">
         <v>0.09606847921069157</v>
@@ -1296,7 +1296,7 @@
         <v>-0.5015961620816233</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4485832354839924</v>
+        <v>-0.4181600802070733</v>
       </c>
       <c r="L17" t="n">
         <v>1.677181455003627</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.4355523799314322</v>
+        <v>-0.4355626368786944</v>
       </c>
       <c r="B18" t="n">
         <v>0.09606847921069157</v>
@@ -1349,7 +1349,7 @@
         <v>-0.6261267654992482</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4485832354839924</v>
+        <v>-0.4181600802070733</v>
       </c>
       <c r="L18" t="n">
         <v>1.677181455003627</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.02377868235614849</v>
+        <v>0.02375208723981349</v>
       </c>
       <c r="B19" t="n">
         <v>0.7710978171778432</v>
@@ -1402,7 +1402,7 @@
         <v>-0.6100583005421354</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L19" t="n">
         <v>-0.5610833718729226</v>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.109366301499116</v>
+        <v>-1.109352591232579</v>
       </c>
       <c r="B20" t="n">
         <v>0.4154371982489139</v>
@@ -1455,7 +1455,7 @@
         <v>1.591321398582332</v>
       </c>
       <c r="K20" t="n">
-        <v>1.386378626072649</v>
+        <v>1.396776542038672</v>
       </c>
       <c r="L20" t="n">
         <v>-0.6882575097636355</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1.317809484276268</v>
+        <v>1.317736861151459</v>
       </c>
       <c r="B21" t="n">
         <v>-0.499118678996904</v>
@@ -1508,7 +1508,7 @@
         <v>-0.6381781142170829</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L21" t="n">
         <v>0.7657668001201835</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.02377868235614849</v>
+        <v>0.02375208723981349</v>
       </c>
       <c r="B22" t="n">
         <v>0.7710978171778432</v>
@@ -1561,7 +1561,7 @@
         <v>-0.6100583005421354</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L22" t="n">
         <v>-0.5610833718729226</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.381387317265527</v>
+        <v>1.38156494217898</v>
       </c>
       <c r="B23" t="n">
         <v>-0.5971068087018129</v>
@@ -1614,7 +1614,7 @@
         <v>-0.6309473049863821</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4169459620088778</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L23" t="n">
         <v>0.9777236966047054</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.2754872468321777</v>
+        <v>-0.275503197213701</v>
       </c>
       <c r="B24" t="n">
         <v>0.01259710946206584</v>
@@ -1667,7 +1667,7 @@
         <v>-0.5256988595172926</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L24" t="n">
         <v>-0.3491264753884007</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2.25336824970097</v>
+        <v>2.253262349233212</v>
       </c>
       <c r="B25" t="n">
         <v>-3.105965848146391</v>
@@ -1720,7 +1720,7 @@
         <v>-0.6353661328495881</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L25" t="n">
         <v>-1.175758371678036</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.317809484276268</v>
+        <v>1.317736861151459</v>
       </c>
       <c r="B26" t="n">
         <v>-0.499118678996904</v>
@@ -1773,7 +1773,7 @@
         <v>-0.6381781142170829</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L26" t="n">
         <v>0.7657668001201835</v>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.8364254208228723</v>
+        <v>-0.8364214189227441</v>
       </c>
       <c r="B27" t="n">
         <v>0.6803680674510756</v>
@@ -1826,7 +1826,7 @@
         <v>1.968930325074485</v>
       </c>
       <c r="K27" t="n">
-        <v>2.525320471176772</v>
+        <v>2.523288928260168</v>
       </c>
       <c r="L27" t="n">
         <v>-1.004073285525573</v>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1658550323054795</v>
+        <v>0.1658233836066257</v>
       </c>
       <c r="B28" t="n">
         <v>0.582379937746166</v>
@@ -1879,7 +1879,7 @@
         <v>-0.6217079376360422</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L28" t="n">
         <v>-0.4720614753494234</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1.109366301499116</v>
+        <v>-1.109352591232579</v>
       </c>
       <c r="B29" t="n">
         <v>0.4154371982489139</v>
@@ -1932,7 +1932,7 @@
         <v>1.591321398582332</v>
       </c>
       <c r="K29" t="n">
-        <v>1.386378626072649</v>
+        <v>1.396776542038672</v>
       </c>
       <c r="L29" t="n">
         <v>-0.6882575097636355</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1.109366301499116</v>
+        <v>-1.109352591232579</v>
       </c>
       <c r="B30" t="n">
         <v>0.4154371982489139</v>
@@ -1985,7 +1985,7 @@
         <v>1.591321398582332</v>
       </c>
       <c r="K30" t="n">
-        <v>1.386378626072649</v>
+        <v>1.396776542038672</v>
       </c>
       <c r="L30" t="n">
         <v>-0.6882575097636355</v>
@@ -2008,7 +2008,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.4355839447377982</v>
+        <v>-0.4355942005623165</v>
       </c>
       <c r="B31" t="n">
         <v>0.09606847921069157</v>
@@ -2038,7 +2038,7 @@
         <v>-0.62210964925997</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.4485832354839924</v>
+        <v>-0.4181600802070733</v>
       </c>
       <c r="L31" t="n">
         <v>1.677181455003627</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1.38126105804005</v>
+        <v>1.38156494217898</v>
       </c>
       <c r="B32" t="n">
         <v>-0.5971068087018129</v>
@@ -2091,7 +2091,7 @@
         <v>-0.6309473049863821</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.2903968681084198</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L32" t="n">
         <v>0.9777236966047054</v>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.1658550323054795</v>
+        <v>0.1658233836066257</v>
       </c>
       <c r="B33" t="n">
         <v>0.582379937746166</v>
@@ -2144,7 +2144,7 @@
         <v>-0.6217079376360422</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L33" t="n">
         <v>-0.4720614753494234</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.1658550323054795</v>
+        <v>0.1658233836066257</v>
       </c>
       <c r="B34" t="n">
         <v>0.582379937746166</v>
@@ -2197,7 +2197,7 @@
         <v>-0.6217079376360422</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L34" t="n">
         <v>-0.4720614753494234</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.317809484276268</v>
+        <v>1.317736861151459</v>
       </c>
       <c r="B35" t="n">
         <v>-0.499118678996904</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6381781142170829</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L35" t="n">
         <v>0.7657668001201835</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1.109366301499116</v>
+        <v>-1.109352591232579</v>
       </c>
       <c r="B36" t="n">
         <v>0.4154371982489139</v>
@@ -2303,7 +2303,7 @@
         <v>1.591321398582332</v>
       </c>
       <c r="K36" t="n">
-        <v>1.386378626072649</v>
+        <v>1.396776542038672</v>
       </c>
       <c r="L36" t="n">
         <v>-0.6882575097636355</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.4366887129607281</v>
+        <v>-0.4366989294892103</v>
       </c>
       <c r="B37" t="n">
         <v>0.09606847921069157</v>
@@ -2356,7 +2356,7 @@
         <v>-0.4815105808852321</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.4485832354839924</v>
+        <v>-0.4181600802070733</v>
       </c>
       <c r="L37" t="n">
         <v>1.677181455003627</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.2754872468321777</v>
+        <v>-0.275503197213701</v>
       </c>
       <c r="B38" t="n">
         <v>0.01259710946206584</v>
@@ -2409,7 +2409,7 @@
         <v>-0.5256988595172926</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L38" t="n">
         <v>-0.3491264753884007</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.02377868235614849</v>
+        <v>0.02375208723981349</v>
       </c>
       <c r="B39" t="n">
         <v>0.7710978171778432</v>
@@ -2462,7 +2462,7 @@
         <v>-0.6100583005421354</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L39" t="n">
         <v>-0.5610833718729226</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1.381576706103741</v>
+        <v>1.38156494217898</v>
       </c>
       <c r="B40" t="n">
         <v>-0.5971068087018129</v>
@@ -2515,7 +2515,7 @@
         <v>-0.6309473049863821</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.6067696028595648</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L40" t="n">
         <v>0.9777236966047054</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.109366301499116</v>
+        <v>-1.109352591232579</v>
       </c>
       <c r="B41" t="n">
         <v>0.4154371982489139</v>
@@ -2568,7 +2568,7 @@
         <v>1.591321398582332</v>
       </c>
       <c r="K41" t="n">
-        <v>1.386378626072649</v>
+        <v>1.396776542038672</v>
       </c>
       <c r="L41" t="n">
         <v>-0.6882575097636355</v>
@@ -2591,7 +2591,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1.109366301499116</v>
+        <v>-1.109352591232579</v>
       </c>
       <c r="B42" t="n">
         <v>0.4154371982489139</v>
@@ -2621,7 +2621,7 @@
         <v>1.591321398582332</v>
       </c>
       <c r="K42" t="n">
-        <v>1.386378626072649</v>
+        <v>1.396776542038672</v>
       </c>
       <c r="L42" t="n">
         <v>-0.6882575097636355</v>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.4362152408651893</v>
+        <v>-0.4362254742348298</v>
       </c>
       <c r="B43" t="n">
         <v>0.09606847921069157</v>
@@ -2674,7 +2674,7 @@
         <v>-0.5417673244744056</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.4485832354839924</v>
+        <v>-0.4181600802070733</v>
       </c>
       <c r="L43" t="n">
         <v>1.677181455003627</v>
@@ -2697,7 +2697,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1.317809484276268</v>
+        <v>1.317736861151459</v>
       </c>
       <c r="B44" t="n">
         <v>-0.499118678996904</v>
@@ -2727,7 +2727,7 @@
         <v>-0.6381781142170829</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L44" t="n">
         <v>0.7657668001201835</v>
@@ -2750,7 +2750,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-1.109366301499116</v>
+        <v>-1.109352591232579</v>
       </c>
       <c r="B45" t="n">
         <v>0.4154371982489139</v>
@@ -2780,7 +2780,7 @@
         <v>1.591321398582332</v>
       </c>
       <c r="K45" t="n">
-        <v>1.386378626072649</v>
+        <v>1.396776542038672</v>
       </c>
       <c r="L45" t="n">
         <v>-0.6882575097636355</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.02377868235614849</v>
+        <v>0.02375208723981349</v>
       </c>
       <c r="B46" t="n">
         <v>0.7710978171778432</v>
@@ -2833,7 +2833,7 @@
         <v>-0.6100583005421354</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L46" t="n">
         <v>-0.5610833718729226</v>
@@ -2856,7 +2856,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.008417420140645662</v>
+        <v>-0.008442870058213873</v>
       </c>
       <c r="B47" t="n">
         <v>0.8037605270794795</v>
@@ -2886,7 +2886,7 @@
         <v>-0.6180925330206918</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.670044149809794</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L47" t="n">
         <v>-0.5759203546268391</v>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-0.4359942872206006</v>
+        <v>-0.4360045284494483</v>
       </c>
       <c r="B48" t="n">
         <v>0.09606847921069157</v>
@@ -2939,7 +2939,7 @@
         <v>-0.5698871381493531</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.4485832354839924</v>
+        <v>-0.4181600802070733</v>
       </c>
       <c r="L48" t="n">
         <v>1.677181455003627</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1.381166363620938</v>
+        <v>1.38156494217898</v>
       </c>
       <c r="B49" t="n">
         <v>-0.5971068087018129</v>
@@ -2992,7 +2992,7 @@
         <v>-0.6309473049863821</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.1954850476830762</v>
+        <v>-0.6372041553056977</v>
       </c>
       <c r="L49" t="n">
         <v>0.9777236966047054</v>
